--- a/data/tags/אלבומים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
+        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-your-favorite-toy/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
+        <v>במשך שני העשורים האחרונים, דייב גרוהל Dave Grohl תמיד מצא רעיון מרכזי שעליו נשען כל אלבום חדש של פו פייטרס Foo Fighters.האלבום In Your Honor היה אלבום כפול שהתפצל בין צד "קשוח” לצד "רך”, ואילו האלבום שאחריו, Echoes, Silence, Patience</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
     </row>
   </sheetData>
